--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413969</v>
+        <v>6413970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>5176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413969</v>
+        <v>6413970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413969</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413969</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413969</v>
+        <v>6413970</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413969</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,39 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R4" t="n">
-        <v>6413992</v>
+        <v>6413970</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +1027,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R5" t="n">
-        <v>6413969</v>
+        <v>6413992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,6 +1103,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34351-2025 artfynd.xlsx
+++ b/artfynd/A 34351-2025 artfynd.xlsx
@@ -921,42 +921,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127172869</v>
+        <v>127172964</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>5176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467155</v>
+        <v>467244</v>
       </c>
       <c r="R4" t="n">
-        <v>6413970</v>
+        <v>6413992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,39 +1029,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127172964</v>
+        <v>127172869</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467244</v>
+        <v>467155</v>
       </c>
       <c r="R5" t="n">
-        <v>6413992</v>
+        <v>6413969</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
